--- a/data/trans_dic/P35-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P35-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,37</t>
+          <t>15,21; 21,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,19; 27,96</t>
+          <t>20,95; 27,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 25,62</t>
+          <t>18,56; 25,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,65; 36,04</t>
+          <t>28,72; 35,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,1; 25,77</t>
+          <t>19,35; 25,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,34; 35,38</t>
+          <t>28,48; 36,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,04; 34,12</t>
+          <t>27,14; 34,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,43; 37,29</t>
+          <t>31,39; 37,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,2; 22,43</t>
+          <t>18,36; 22,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,53; 30,67</t>
+          <t>25,65; 30,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,88; 28,72</t>
+          <t>23,9; 28,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,97; 35,73</t>
+          <t>30,47; 35,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 18,54</t>
+          <t>13,57; 18,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,32; 29,02</t>
+          <t>23,3; 28,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,82; 31,65</t>
+          <t>25,8; 31,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,76; 35,58</t>
+          <t>12,6; 35,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,57; 26,18</t>
+          <t>20,63; 26,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,81; 37,99</t>
+          <t>31,98; 37,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,38; 40,58</t>
+          <t>34,31; 40,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,67; 43,9</t>
+          <t>38,07; 43,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,81; 21,62</t>
+          <t>17,85; 21,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,25; 32,72</t>
+          <t>28,23; 32,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,8; 35,14</t>
+          <t>30,96; 35,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,7; 38,35</t>
+          <t>22,5; 38,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,81; 23,66</t>
+          <t>17,05; 23,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,07; 30,08</t>
+          <t>23,21; 30,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,9; 36,15</t>
+          <t>29,05; 36,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,23; 37,17</t>
+          <t>29,45; 37,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,58; 29,23</t>
+          <t>22,22; 28,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,52; 38,82</t>
+          <t>31,6; 38,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,84; 41,04</t>
+          <t>34,13; 40,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 36,34</t>
+          <t>13,38; 35,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,53; 25,21</t>
+          <t>20,25; 25,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,32; 33,28</t>
+          <t>28,13; 33,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,69; 37,69</t>
+          <t>32,67; 37,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,91; 35,13</t>
+          <t>20,13; 34,85</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,47; 19,22</t>
+          <t>14,61; 19,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,06; 30,13</t>
+          <t>23,63; 29,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,8; 30,39</t>
+          <t>24,46; 30,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,94; 38,38</t>
+          <t>32,2; 38,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 19,48</t>
+          <t>14,51; 19,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,94; 37,95</t>
+          <t>31,71; 37,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,97; 36,19</t>
+          <t>30,22; 36,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,5; 38,85</t>
+          <t>28,37; 39,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,17; 18,48</t>
+          <t>15,25; 18,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,04; 33,44</t>
+          <t>29,26; 33,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,35; 32,77</t>
+          <t>28,45; 32,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,18; 37,86</t>
+          <t>31,08; 37,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,12; 18,85</t>
+          <t>16,32; 18,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,59</t>
+          <t>24,28; 27,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,19; 29,48</t>
+          <t>26,3; 29,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,92; 34,82</t>
+          <t>24,37; 34,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,04; 22,99</t>
+          <t>20,12; 22,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,68; 36,02</t>
+          <t>32,68; 36,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,12; 36,65</t>
+          <t>32,85; 36,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,54; 37,25</t>
+          <t>27,51; 37,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,59</t>
+          <t>18,61; 20,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,16; 31,54</t>
+          <t>29,24; 31,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,3; 32,64</t>
+          <t>30,31; 32,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,57; 35,27</t>
+          <t>28,79; 35,56</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico</t>
+          <t>Población a la que su médico le ha aconsejado hacer algún tipo de ejercicio físico (tasa de respuesta: 97,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>103230; 141359</t>
+          <t>100614; 139452</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>146878; 193770</t>
+          <t>145228; 192634</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125040; 170517</t>
+          <t>123510; 166879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>182075; 228989</t>
+          <t>182524; 228492</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>124990; 168653</t>
+          <t>126630; 167011</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>191368; 238942</t>
+          <t>192346; 243135</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>180752; 228100</t>
+          <t>181425; 230166</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>212039; 251568</t>
+          <t>211785; 250440</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>239457; 295093</t>
+          <t>241582; 299653</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>349309; 419754</t>
+          <t>350956; 419971</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>318559; 383164</t>
+          <t>318903; 384241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>405783; 468121</t>
+          <t>399178; 464160</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>126108; 171828</t>
+          <t>125717; 168559</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>232380; 289130</t>
+          <t>232143; 287322</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>261517; 320593</t>
+          <t>261377; 321685</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>176016; 424423</t>
+          <t>150278; 425787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>190091; 241998</t>
+          <t>190691; 242923</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>320476; 382748</t>
+          <t>322233; 380147</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>353103; 416706</t>
+          <t>352373; 416981</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>370281; 420338</t>
+          <t>364587; 419117</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>329586; 400115</t>
+          <t>330362; 399613</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>566162; 655607</t>
+          <t>565681; 652118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>628223; 716901</t>
+          <t>631463; 718663</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>488248; 824769</t>
+          <t>483796; 823298</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>106349; 149650</t>
+          <t>107873; 148645</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>171237; 223323</t>
+          <t>172345; 223848</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>217963; 272595</t>
+          <t>219053; 272337</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>205945; 261955</t>
+          <t>207512; 262626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>143280; 185433</t>
+          <t>140953; 183550</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>239714; 295231</t>
+          <t>240318; 293356</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>260847; 316392</t>
+          <t>263072; 315496</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>130192; 338913</t>
+          <t>124755; 334215</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>260076; 319488</t>
+          <t>256570; 318583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>425572; 500156</t>
+          <t>422734; 501113</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>498480; 574743</t>
+          <t>498215; 571716</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>309573; 575267</t>
+          <t>329535; 570658</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>131194; 174240</t>
+          <t>132427; 175576</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>215432; 269874</t>
+          <t>211638; 267634</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>224872; 275627</t>
+          <t>221788; 277138</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>296073; 355752</t>
+          <t>298450; 355895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>145880; 193819</t>
+          <t>144356; 190687</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>322205; 382861</t>
+          <t>319866; 380898</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>308595; 372618</t>
+          <t>311130; 372799</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>311008; 423941</t>
+          <t>309630; 425833</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>288517; 351302</t>
+          <t>289981; 354799</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>553096; 636832</t>
+          <t>557258; 638471</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>549086; 634618</t>
+          <t>551009; 635874</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>629343; 764122</t>
+          <t>627278; 761852</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>504055; 589433</t>
+          <t>510422; 590682</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>808315; 918082</t>
+          <t>808044; 923851</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>874749; 984567</t>
+          <t>878132; 981053</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>862249; 1204823</t>
+          <t>843324; 1198696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>643049; 737446</t>
+          <t>645355; 734471</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1128156; 1243553</t>
+          <t>1128096; 1245567</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1157730; 1281273</t>
+          <t>1148481; 1268184</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1043356; 1361965</t>
+          <t>1005768; 1371118</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1182969; 1304283</t>
+          <t>1178787; 1297968</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1976645; 2138551</t>
+          <t>1982308; 2128182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2070915; 2231270</t>
+          <t>2071546; 2225499</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2032995; 2509442</t>
+          <t>2048831; 2530350</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P35-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P35-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 21,09</t>
+          <t>15,23; 20,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,95; 27,79</t>
+          <t>20,95; 27,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,56; 25,07</t>
+          <t>18,82; 25,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,72; 35,96</t>
+          <t>28,9; 36,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,35; 25,52</t>
+          <t>19,24; 25,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,48; 36,0</t>
+          <t>28,4; 36,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,14; 34,43</t>
+          <t>27,06; 34,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,39; 37,12</t>
+          <t>31,58; 37,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,36; 22,77</t>
+          <t>17,84; 22,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,65; 30,69</t>
+          <t>25,59; 30,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,9; 28,8</t>
+          <t>23,98; 28,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,47; 35,43</t>
+          <t>31,16; 35,73</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,57; 18,19</t>
+          <t>13,56; 18,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,3; 28,84</t>
+          <t>23,31; 29,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,8; 31,76</t>
+          <t>25,42; 31,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,6; 35,69</t>
+          <t>31,91; 38,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,63; 26,29</t>
+          <t>20,58; 26,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,98; 37,73</t>
+          <t>31,83; 38,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,31; 40,6</t>
+          <t>34,25; 40,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,07; 43,77</t>
+          <t>38,27; 43,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 21,59</t>
+          <t>17,64; 21,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,23; 32,54</t>
+          <t>28,29; 32,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,96; 35,23</t>
+          <t>31,0; 35,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,5; 38,29</t>
+          <t>36,0; 40,27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>34,74%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 23,5</t>
+          <t>17,15; 23,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,21; 30,15</t>
+          <t>22,68; 30,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,05; 36,11</t>
+          <t>28,93; 36,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,45; 37,27</t>
+          <t>29,29; 37,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,22; 28,93</t>
+          <t>22,3; 28,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,6; 38,57</t>
+          <t>31,7; 39,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,13; 40,93</t>
+          <t>33,8; 40,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 35,84</t>
+          <t>33,01; 39,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,25; 25,14</t>
+          <t>20,57; 25,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,13; 33,34</t>
+          <t>28,45; 33,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,67; 37,49</t>
+          <t>32,61; 37,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,13; 34,85</t>
+          <t>32,39; 37,3</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 19,37</t>
+          <t>14,77; 19,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,63; 29,88</t>
+          <t>23,83; 30,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,46; 30,56</t>
+          <t>24,7; 30,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,2; 38,4</t>
+          <t>33,11; 39,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,51; 19,17</t>
+          <t>14,63; 19,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,71; 37,76</t>
+          <t>31,87; 37,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,22; 36,21</t>
+          <t>29,86; 35,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,37; 39,02</t>
+          <t>36,12; 41,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,25; 18,66</t>
+          <t>15,2; 18,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,26; 33,53</t>
+          <t>29,0; 33,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,45; 32,84</t>
+          <t>28,18; 32,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,08; 37,75</t>
+          <t>34,96; 39,42</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 18,89</t>
+          <t>16,28; 18,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,28; 27,76</t>
+          <t>24,29; 27,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,3; 29,38</t>
+          <t>26,35; 29,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,37; 34,65</t>
+          <t>32,68; 36,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,12; 22,89</t>
+          <t>20,18; 23,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,68; 36,08</t>
+          <t>32,8; 36,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,85; 36,28</t>
+          <t>33,29; 36,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,51; 37,5</t>
+          <t>36,56; 39,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,61; 20,49</t>
+          <t>18,61; 20,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,24; 31,39</t>
+          <t>29,17; 31,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,31; 32,56</t>
+          <t>30,37; 32,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,79; 35,56</t>
+          <t>35,18; 37,41</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>204817</t>
+          <t>223021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>231123</t>
+          <t>251905</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>435941</t>
+          <t>474926</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>100614; 139452</t>
+          <t>100699; 138785</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145228; 192634</t>
+          <t>145232; 192748</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123510; 166879</t>
+          <t>125222; 169050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>182524; 228492</t>
+          <t>199609; 248763</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>126630; 167011</t>
+          <t>125948; 167833</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>192346; 243135</t>
+          <t>191816; 243101</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>181425; 230166</t>
+          <t>180910; 228636</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>211785; 250440</t>
+          <t>231128; 274579</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>241582; 299653</t>
+          <t>234725; 294106</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>350956; 419971</t>
+          <t>350138; 416870</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>318903; 384241</t>
+          <t>319876; 382581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>399178; 464160</t>
+          <t>443292; 508272</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>325731</t>
+          <t>367521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>392567</t>
+          <t>437140</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>718298</t>
+          <t>804661</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125717; 168559</t>
+          <t>125643; 170982</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>232143; 287322</t>
+          <t>232315; 288946</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>261377; 321685</t>
+          <t>257510; 314766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>150278; 425787</t>
+          <t>334749; 404757</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>190691; 242923</t>
+          <t>190170; 243987</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>322233; 380147</t>
+          <t>320674; 382929</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>352373; 416981</t>
+          <t>351696; 416080</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>364587; 419117</t>
+          <t>409528; 467738</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>330362; 399613</t>
+          <t>326418; 397773</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>565681; 652118</t>
+          <t>566960; 650141</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>631463; 718663</t>
+          <t>632376; 719371</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>483796; 823298</t>
+          <t>762881; 853441</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>234359</t>
+          <t>266300</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>252674</t>
+          <t>294577</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>487033</t>
+          <t>560877</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>107873; 148645</t>
+          <t>108514; 151320</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>172345; 223848</t>
+          <t>168370; 223279</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>219053; 272337</t>
+          <t>218148; 272623</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>207512; 262626</t>
+          <t>235203; 298684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>140953; 183550</t>
+          <t>141476; 183041</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>240318; 293356</t>
+          <t>241050; 296827</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>263072; 315496</t>
+          <t>260523; 315629</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>124755; 334215</t>
+          <t>267913; 319663</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>256570; 318583</t>
+          <t>260637; 319005</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>422734; 501113</t>
+          <t>427574; 501937</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>498215; 571716</t>
+          <t>497237; 573858</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>329535; 570658</t>
+          <t>523046; 602281</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326756</t>
+          <t>357729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>387269</t>
+          <t>429489</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>714025</t>
+          <t>787219</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>132427; 175576</t>
+          <t>133893; 174487</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>211638; 267634</t>
+          <t>213414; 271762</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>221788; 277138</t>
+          <t>224021; 276796</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>298450; 355895</t>
+          <t>327838; 388268</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>144356; 190687</t>
+          <t>145514; 193330</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>319866; 380898</t>
+          <t>321476; 381596</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>311130; 372799</t>
+          <t>307437; 369479</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>309630; 425833</t>
+          <t>403453; 458595</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>289981; 354799</t>
+          <t>288945; 352337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>557258; 638471</t>
+          <t>552342; 640583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>551009; 635874</t>
+          <t>545634; 631977</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>627278; 761852</t>
+          <t>736633; 830514</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1091663</t>
+          <t>1214570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1263634</t>
+          <t>1413111</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2355296</t>
+          <t>2627681</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>510422; 590682</t>
+          <t>508961; 587680</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>808044; 923851</t>
+          <t>808272; 912678</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>878132; 981053</t>
+          <t>879891; 986707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>843324; 1198696</t>
+          <t>1154652; 1279714</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>645355; 734471</t>
+          <t>647402; 744599</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1128096; 1245567</t>
+          <t>1132348; 1251401</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1148481; 1268184</t>
+          <t>1163670; 1273608</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1005768; 1371118</t>
+          <t>1363945; 1468276</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1178787; 1297968</t>
+          <t>1179306; 1298809</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1982308; 2128182</t>
+          <t>1977435; 2130614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2071546; 2225499</t>
+          <t>2076240; 2232777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2048831; 2530350</t>
+          <t>2555255; 2717022</t>
         </is>
       </c>
     </row>
